--- a/data_suivi/suivi_suggestions.xlsx
+++ b/data_suivi/suivi_suggestions.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -509,6 +509,46 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>FAQ ajoutée + macro MAC-016 : procédure de dépannage capsule (nettoyage des contacts, réinitialisation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Code promo non appliqué</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fait</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Macro MAC-017 : vérification de la validité du code + recrédit immédiat si erreur côté Emyria</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Parfum délivré en excès</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fait</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Macro MAC-018 : réglage intensité/mode diffusion via l'app — adoptée par l'équipe (67% des tickets) mais CSAT quasi inchangé (3.51 -&gt; 3.44) : le réglage app ne résout pas le problème pour une partie des clients, la cause est probablement matérielle (à creuser avec le produit).</t>
         </is>
       </c>
     </row>

--- a/data_suivi/suivi_suggestions.xlsx
+++ b/data_suivi/suivi_suggestions.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Macro MAC-018 : réglage intensité/mode diffusion via l'app — adoptée par l'équipe (67% des tickets) mais CSAT quasi inchangé (3.51 -&gt; 3.44) : le réglage app ne résout pas le problème pour une partie des clients, la cause est probablement matérielle (à creuser avec le produit).</t>
+          <t>Macro MAC-018 : réglage intensité/mode diffusion via l'app, mis en place pour tenter de réduire les réclamations liées à un parfum délivré en excès. Hypothèse de l'équipe au moment de l'action : le réglage applicatif ne suffit probablement pas à couvrir tous les cas, la cause étant possiblement matérielle (à creuser avec le produit).</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>notes : libre (ex : lien vers la macro, qui l'a créée...).</t>
+          <t>notes : libre (ex : lien vers la macro, qui l'a créée...). Ne pas y saisir de KPI ou de valeurs avant/après calculables par Emyria (CSAT, volumes, taux) : ces valeurs sont produites automatiquement à partir de date_action.</t>
         </is>
       </c>
     </row>
